--- a/output/pdf_financials_xlsx/AVU.xlsx
+++ b/output/pdf_financials_xlsx/AVU.xlsx
@@ -5689,34 +5689,34 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.046567</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.179864</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.084186</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.080183</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.42729</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.141772</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.591348</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.119842</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.675064</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.782381</v>
       </c>
       <c r="L92" s="1" t="inlineStr">
         <is>
@@ -5724,19 +5724,19 @@
         </is>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.980564</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.641733</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.642877</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.778743</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>8.013771</v>
       </c>
     </row>
     <row r="93">
@@ -11144,7 +11144,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11980,7 +11984,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -13084,7 +13092,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -13738,7 +13750,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -14646,7 +14662,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -17332,7 +17352,11 @@
           <t>Reserves 6 1,179,864</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
         <v>0.046567</v>
       </c>
@@ -19000,7 +19024,11 @@
           <t>Reserves (Note 6) 1,061,503</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="n">
         <v>0.046567</v>
       </c>

--- a/output/pdf_financials_xlsx/AVU.xlsx
+++ b/output/pdf_financials_xlsx/AVU.xlsx
@@ -1005,34 +1005,34 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002038</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.020572</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.011828</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003141</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.008956</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002508</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.003056</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.002068</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001181</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000148</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.002607</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000491</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -1919,31 +1919,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.117206</v>
+        <v>-2.137778</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.529054</v>
+        <v>-1.540882</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.882598</v>
+        <v>-1.885739</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.250956</v>
+        <v>-1.259912</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.54893</v>
+        <v>-1.551438</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.872121</v>
+        <v>-1.875177</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.906297</v>
+        <v>-1.908365</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.885332</v>
+        <v>-1.886513</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.097599</v>
+        <v>-2.097747</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.138911</v>
@@ -1952,13 +1952,13 @@
         <v>-0.005997</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.329789</v>
+        <v>-0.332396</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.056781</v>
+        <v>-0.057272</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.04663</v>
+        <v>-0.046635</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-0.275016</v>
@@ -2031,31 +2031,31 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.106354</v>
+        <v>-2.126926</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.502152</v>
+        <v>-1.51398</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.882598</v>
+        <v>-1.885739</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.250956</v>
+        <v>-1.259912</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.54893</v>
+        <v>-1.551438</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.872121</v>
+        <v>-1.875177</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.906297</v>
+        <v>-1.908365</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.885332</v>
+        <v>-1.886513</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.097599</v>
+        <v>-2.097747</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.138911</v>
@@ -2064,13 +2064,13 @@
         <v>-0.005997</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.329789</v>
+        <v>-0.332396</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.056781</v>
+        <v>-0.057272</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.04663</v>
+        <v>-0.046635</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-0.275016</v>
@@ -2330,25 +2330,25 @@
         <v>0.75024</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.439154</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.7619320000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.161926</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.518196</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.182794</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.106288</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.058343</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -2356,19 +2356,19 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.139164</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.307531</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.121745</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.141011</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.493359</v>
       </c>
     </row>
     <row r="35">
@@ -2444,25 +2444,25 @@
         <v>0.75024</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.439154</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.7619320000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.161926</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.518196</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.182794</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.106288</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.058343</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.139164</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.307531</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.121745</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.141011</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.493359</v>
       </c>
     </row>
     <row r="37">
@@ -3128,25 +3128,25 @@
         <v>0.6551</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.483323</v>
+        <v>1.044169</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.497694</v>
+        <v>0.735762</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.833615</v>
+        <v>0.671689</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.716944</v>
+        <v>0.198748</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.457901</v>
+        <v>0.275107</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.237827</v>
+        <v>0.131539</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.138341</v>
+        <v>0.079998</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -3154,19 +3154,19 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.15216</v>
+        <v>0.012996</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.352041</v>
+        <v>0.04451</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.214937</v>
+        <v>0.093192</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.181172</v>
+        <v>0.040161</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.571717</v>
+        <v>0.078358</v>
       </c>
     </row>
     <row r="49">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -27198,7 +27198,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -39672,7 +39672,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E330" s="5" t="n">
@@ -43188,7 +43188,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E366" s="5" t="n">

--- a/output/pdf_financials_xlsx/AVU.xlsx
+++ b/output/pdf_financials_xlsx/AVU.xlsx
@@ -38400,7 +38400,11 @@
           <t>Director fees -</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -41790,7 +41794,11 @@
           <t>Director fees 3,847</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
